--- a/BOM/sensor_board.xlsx
+++ b/BOM/sensor_board.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tanya\Documents\LHR\blackbodies v1\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8B7208-46D1-4E6C-89B1-B45671E37529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F34F71-9EC1-4082-AFE7-C9355E988246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C3AC1174-7626-49F8-AFAA-A525B3B7E685}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="1" xr2:uid="{C3AC1174-7626-49F8-AFAA-A525B3B7E685}"/>
   </bookViews>
   <sheets>
     <sheet name="Full BOM" sheetId="1" r:id="rId1"/>
+    <sheet name="Shortened BOM" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
   <si>
     <t>Reference</t>
   </si>
@@ -34,12 +35,6 @@
     <t>BlackbodyC1</t>
   </si>
   <si>
-    <t>Conn_01x04</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 105405-2204</t>
-  </si>
-  <si>
     <t>C4</t>
   </si>
   <si>
@@ -65,6 +60,12 @@
   </si>
   <si>
     <t>Qty (x 6 for 6 boards)</t>
+  </si>
+  <si>
+    <t>105405-2204</t>
+  </si>
+  <si>
+    <t>Conn_02x02</t>
   </si>
 </sst>
 </file>
@@ -548,8 +549,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -927,6 +931,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93B89D4-AAF8-430A-8106-F8EEF75F8219}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="17.9296875" customWidth="1"/>
+    <col min="2" max="2" width="15.46484375" customWidth="1"/>
+    <col min="3" max="3" width="19.53125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -936,7 +945,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -947,55 +956,112 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D947F98-B07D-4E91-A97D-3BDAFC003356}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="17.9296875" customWidth="1"/>
+    <col min="2" max="2" width="15.46484375" customWidth="1"/>
+    <col min="3" max="3" width="19.53125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="C5">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
-        <v>13</v>
+      <c r="D3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
